--- a/data/trans_dic/IP31KM03_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM03_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,26; 90,4</t>
+          <t>77,95; 89,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,73; 89,63</t>
+          <t>78,28; 90,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,7; 88,57</t>
+          <t>80,6; 88,65</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,14; 87,47</t>
+          <t>71,99; 87,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,94; 87,72</t>
+          <t>74,37; 87,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,73; 85,75</t>
+          <t>75,67; 86,34</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,85; 95,66</t>
+          <t>77,83; 92,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,04; 93,17</t>
+          <t>80,32; 95,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,9; 92,33</t>
+          <t>81,94; 92,8</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,39; 90,55</t>
+          <t>77,86; 87,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,6; 87,77</t>
+          <t>79,01; 88,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,49; 87,87</t>
+          <t>79,64; 86,68</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,7; 88,68</t>
+          <t>80,94; 91,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81,26; 91,55</t>
+          <t>76,14; 87,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,37; 89,23</t>
+          <t>80,4; 88,94</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76,92; 91,14</t>
+          <t>65,75; 85,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,92; 85,2</t>
+          <t>75,75; 91,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,76; 87,01</t>
+          <t>73,57; 86,47</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>83,83%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82,05; 87,55</t>
+          <t>80,71; 85,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>81,14; 86,3</t>
+          <t>81,56; 86,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82,35; 86,16</t>
+          <t>81,74; 85,65</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>129</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86887</t>
+          <t>102461</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114316</t>
+          <t>85384</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>201203</t>
+          <t>187845</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79594; 91943</t>
+          <t>94482; 108651</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106425; 121164</t>
+          <t>78553; 90430</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>191175; 209816</t>
+          <t>178580; 196421</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>111</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>76176</t>
+          <t>72785</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76061</t>
+          <t>77882</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>152238</t>
+          <t>150667</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69242; 81691</t>
+          <t>64707; 78655</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67409; 82201</t>
+          <t>70958; 83555</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141689; 160436</t>
+          <t>140211; 159973</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44874</t>
+          <t>48527</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54271</t>
+          <t>46636</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99145</t>
+          <t>95163</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39996; 47917</t>
+          <t>43466; 51836</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49268; 58077</t>
+          <t>41773; 49797</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92078; 103802</t>
+          <t>88377; 100093</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>226</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>184242</t>
+          <t>164392</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>176861</t>
+          <t>148261</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361103</t>
+          <t>312653</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>173267; 195168</t>
+          <t>153620; 173242</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>165017; 186653</t>
+          <t>139557; 155778</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>344675; 376254</t>
+          <t>297804; 324138</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>145</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>96090</t>
+          <t>126319</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>139360</t>
+          <t>95205</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>235450</t>
+          <t>221524</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>88599; 102439</t>
+          <t>117842; 133185</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>129570; 145979</t>
+          <t>87914; 101448</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>223733; 245352</t>
+          <t>209877; 232183</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>84</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>58784</t>
+          <t>50313</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>53270</t>
+          <t>59824</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112053</t>
+          <t>110138</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52992; 62794</t>
+          <t>43307; 56072</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>46195; 58815</t>
+          <t>53296; 64478</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>103108; 120013</t>
+          <t>100220; 117795</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>759</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>547052</t>
+          <t>564798</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>614139</t>
+          <t>513193</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1161191</t>
+          <t>1077991</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>529350; 564817</t>
+          <t>545337; 580834</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>594234; 632027</t>
+          <t>497704; 529152</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1134372; 1186824</t>
+          <t>1051172; 1101337</t>
         </is>
       </c>
     </row>
